--- a/data/templates/ENA-Enrichment.xlsx
+++ b/data/templates/ENA-Enrichment.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studies" sheetId="1" r:id="R294837577c874a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publications" sheetId="2" r:id="Re623a7f521554032"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study hierarchy" sheetId="3" r:id="R3c4a38f99ebb46c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="4" r:id="R74b2b818123e423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiments" sheetId="5" r:id="R56e0cc78f1aa4c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="6" r:id="R6d34861645f64974"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File listings" sheetId="7" r:id="R00d01b7cf5d84e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studies" sheetId="1" r:id="R70521125106147c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publications" sheetId="2" r:id="R3d3fedf0ed32462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study hierarchy" sheetId="3" r:id="R71ae63b1d7334514"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="4" r:id="Rb45b7a44a03e40e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiments" sheetId="5" r:id="R77cc51a2f4a24a08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="6" r:id="Rbac355da6ea84c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File listings" sheetId="7" r:id="R4249fb22250f491c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,6 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="@"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -27,7 +30,6 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -51,13 +53,19 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -262,57 +270,41 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="55" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="90" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="60" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="80" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Study accession</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>SRA study accession</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>Search PMID</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>ENA PMID</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Study title</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Organism</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>Native record type</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Samples in report</x:v>
       </x:c>
-      <x:c r="I1" s="3" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Experiments in report</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Runs in report</x:v>
       </x:c>
-      <x:c r="K1" s="3" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Study description</x:v>
       </x:c>
-      <x:c r="L1" s="3" t="str">
-        <x:v>Source URL</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -323,39 +315,39 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="52" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>PMID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>DOI</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>PMCID</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Publication title</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Authors</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Journal</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Publication date</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Retrieval result</x:v>
       </x:c>
     </x:row>
@@ -368,19 +360,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Study accession</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Relationship</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Related study accession</x:v>
       </x:c>
     </x:row>
@@ -393,31 +385,31 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="80" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Sample accession</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Sample title</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Sample description</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Organism</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Reporting studies</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Run accessions</x:v>
       </x:c>
     </x:row>
@@ -430,55 +422,55 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="90" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="25" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="80" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="25" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Experiment accession</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Experiment title</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Sample accession</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Library strategy</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Library source</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Library selection</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Library layout</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Instrument platform</x:v>
       </x:c>
-      <x:c r="I1" s="3" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>Instrument model</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>Library construction protocol</x:v>
       </x:c>
-      <x:c r="K1" s="3" t="str">
+      <x:c r="K1" s="5" t="str">
         <x:v>Reporting studies</x:v>
       </x:c>
-      <x:c r="L1" s="3" t="str">
+      <x:c r="L1" s="5" t="str">
         <x:v>Run accessions</x:v>
       </x:c>
     </x:row>
@@ -491,39 +483,39 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Run accession</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Native study accession</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>SRA study accession</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Sample accession</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Experiment accession</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Read count</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Base count</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Reporting studies</x:v>
       </x:c>
     </x:row>
@@ -536,43 +528,43 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Run accession</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Native study accession</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Sample accession</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Experiment accession</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>File position</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Native FTP location</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>MD5 checksum</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Size (bytes)</x:v>
       </x:c>
-      <x:c r="I1" s="3" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>File format</x:v>
       </x:c>
     </x:row>
